--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/205.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/205.xlsx
@@ -426,13 +426,13 @@
         <v>-13.55364127155687</v>
       </c>
       <c r="E2">
-        <v>-16.07967135535145</v>
+        <v>-17.21225629009183</v>
       </c>
       <c r="F2">
-        <v>2.617299058327307</v>
+        <v>0.2385110088065555</v>
       </c>
       <c r="G2">
-        <v>-8.938914409257261</v>
+        <v>-12.04858597684209</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-13.27333076883365</v>
       </c>
       <c r="E3">
-        <v>-15.65946972370571</v>
+        <v>-17.14385821867997</v>
       </c>
       <c r="F3">
-        <v>2.698237516547672</v>
+        <v>0.2124455849972953</v>
       </c>
       <c r="G3">
-        <v>-9.109086381612419</v>
+        <v>-9.040283313669745</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.90548272868401</v>
       </c>
       <c r="E4">
-        <v>-16.7094688779682</v>
+        <v>-19.3208677561794</v>
       </c>
       <c r="F4">
-        <v>2.617153357383087</v>
+        <v>0.7091694024041739</v>
       </c>
       <c r="G4">
-        <v>-8.444894940613979</v>
+        <v>-10.3369677221281</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.47712420318195</v>
       </c>
       <c r="E5">
-        <v>-17.24104379935859</v>
+        <v>-18.23318264122508</v>
       </c>
       <c r="F5">
-        <v>3.021166238647183</v>
+        <v>0.6028251338883305</v>
       </c>
       <c r="G5">
-        <v>-9.136891653596757</v>
+        <v>-10.57113916084845</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.98722948776438</v>
       </c>
       <c r="E6">
-        <v>-19.06628600441619</v>
+        <v>-20.05813049547218</v>
       </c>
       <c r="F6">
-        <v>2.858250411125927</v>
+        <v>0.4990733919560614</v>
       </c>
       <c r="G6">
-        <v>-8.739983727802457</v>
+        <v>-10.35947943179515</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.44294601756588</v>
       </c>
       <c r="E7">
-        <v>-18.14861791760584</v>
+        <v>-19.91176568707027</v>
       </c>
       <c r="F7">
-        <v>3.166647047745366</v>
+        <v>0.4686242701728649</v>
       </c>
       <c r="G7">
-        <v>-8.590489422885588</v>
+        <v>-8.68850143412125</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.84945303935003</v>
       </c>
       <c r="E8">
-        <v>-18.39459556875448</v>
+        <v>-22.66402274929006</v>
       </c>
       <c r="F8">
-        <v>2.966775442687331</v>
+        <v>0.947301758673311</v>
       </c>
       <c r="G8">
-        <v>-8.591439549455359</v>
+        <v>-9.104352301491261</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.22327955115165</v>
       </c>
       <c r="E9">
-        <v>-20.9434833917638</v>
+        <v>-21.53369752307951</v>
       </c>
       <c r="F9">
-        <v>2.720756230959305</v>
+        <v>0.7415007586678702</v>
       </c>
       <c r="G9">
-        <v>-7.555877730952556</v>
+        <v>-9.184924358826043</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.579479992341598</v>
       </c>
       <c r="E10">
-        <v>-19.7594051790822</v>
+        <v>-22.51535747609225</v>
       </c>
       <c r="F10">
-        <v>3.253217164201033</v>
+        <v>0.9388336831434563</v>
       </c>
       <c r="G10">
-        <v>-6.625922315152505</v>
+        <v>-7.209349687174884</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.929779556857094</v>
       </c>
       <c r="E11">
-        <v>-20.94211579261349</v>
+        <v>-22.4109489793714</v>
       </c>
       <c r="F11">
-        <v>3.463202315235064</v>
+        <v>1.226510695271201</v>
       </c>
       <c r="G11">
-        <v>-5.759449920613518</v>
+        <v>-7.134137403068181</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.289299820637122</v>
       </c>
       <c r="E12">
-        <v>-20.89151009557777</v>
+        <v>-23.75633596468023</v>
       </c>
       <c r="F12">
-        <v>3.528514347187787</v>
+        <v>1.461616589535933</v>
       </c>
       <c r="G12">
-        <v>-5.822750861869922</v>
+        <v>-6.997809137760994</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.671794671836367</v>
       </c>
       <c r="E13">
-        <v>-22.96100007471308</v>
+        <v>-24.24969056544587</v>
       </c>
       <c r="F13">
-        <v>3.335440007918818</v>
+        <v>1.842445599903911</v>
       </c>
       <c r="G13">
-        <v>-5.312026380435477</v>
+        <v>-7.600066892810748</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.105865975469714</v>
       </c>
       <c r="E14">
-        <v>-23.00961777165943</v>
+        <v>-24.76801970036382</v>
       </c>
       <c r="F14">
-        <v>3.741649489287628</v>
+        <v>2.163640164026016</v>
       </c>
       <c r="G14">
-        <v>-5.316296984181137</v>
+        <v>-6.528728008665042</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.608251883266072</v>
       </c>
       <c r="E15">
-        <v>-22.90947962592782</v>
+        <v>-27.46098998087519</v>
       </c>
       <c r="F15">
-        <v>4.103114527427527</v>
+        <v>1.554510443711949</v>
       </c>
       <c r="G15">
-        <v>-4.471614600381633</v>
+        <v>-5.927513075460158</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.187813494000557</v>
       </c>
       <c r="E16">
-        <v>-25.34436311579404</v>
+        <v>-26.08778005126324</v>
       </c>
       <c r="F16">
-        <v>4.673757026584584</v>
+        <v>2.323567538484838</v>
       </c>
       <c r="G16">
-        <v>-4.095718707125086</v>
+        <v>-6.332895997834994</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.853053697772959</v>
       </c>
       <c r="E17">
-        <v>-24.90935790261722</v>
+        <v>-27.16582857352925</v>
       </c>
       <c r="F17">
-        <v>4.175584910118037</v>
+        <v>2.310986578692587</v>
       </c>
       <c r="G17">
-        <v>-3.446454515963221</v>
+        <v>-5.330022505986956</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.609580333879404</v>
       </c>
       <c r="E18">
-        <v>-24.83977789948937</v>
+        <v>-26.9022487439128</v>
       </c>
       <c r="F18">
-        <v>4.794964375116828</v>
+        <v>2.574054384600318</v>
       </c>
       <c r="G18">
-        <v>-3.485850007880548</v>
+        <v>-4.982398671635784</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.461095369333629</v>
       </c>
       <c r="E19">
-        <v>-26.48765336308855</v>
+        <v>-27.8869563599327</v>
       </c>
       <c r="F19">
-        <v>4.821879457149721</v>
+        <v>2.083724779827026</v>
       </c>
       <c r="G19">
-        <v>-3.329959728981807</v>
+        <v>-5.931167917735514</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.400323104375745</v>
       </c>
       <c r="E20">
-        <v>-27.73184706822197</v>
+        <v>-29.5783549872196</v>
       </c>
       <c r="F20">
-        <v>4.837955655897346</v>
+        <v>3.224458648482567</v>
       </c>
       <c r="G20">
-        <v>-2.357731957190802</v>
+        <v>-4.92940676918867</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.41727373812686</v>
       </c>
       <c r="E21">
-        <v>-28.42805919063522</v>
+        <v>-28.88812497897048</v>
       </c>
       <c r="F21">
-        <v>4.709938371928714</v>
+        <v>2.966219561911011</v>
       </c>
       <c r="G21">
-        <v>-2.176701395466836</v>
+        <v>-4.090256306985289</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.501753885138823</v>
       </c>
       <c r="E22">
-        <v>-28.08889912983075</v>
+        <v>-30.22514560855014</v>
       </c>
       <c r="F22">
-        <v>4.643284941065614</v>
+        <v>2.516656131107046</v>
       </c>
       <c r="G22">
-        <v>-2.213627220411867</v>
+        <v>-4.78641768625647</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.648936236667728</v>
       </c>
       <c r="E23">
-        <v>-28.67824832261099</v>
+        <v>-30.01769395002176</v>
       </c>
       <c r="F23">
-        <v>5.146792562761277</v>
+        <v>3.098978461390469</v>
       </c>
       <c r="G23">
-        <v>-2.652694943648786</v>
+        <v>-4.123623295475603</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.848303832517999</v>
       </c>
       <c r="E24">
-        <v>-29.7930793750043</v>
+        <v>-31.6104624134216</v>
       </c>
       <c r="F24">
-        <v>5.393698649801949</v>
+        <v>2.783814649394357</v>
       </c>
       <c r="G24">
-        <v>-1.634626047775493</v>
+        <v>-2.374115847064655</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.082146127677149</v>
       </c>
       <c r="E25">
-        <v>-30.25293911777221</v>
+        <v>-30.74879343619009</v>
       </c>
       <c r="F25">
-        <v>5.533416353073848</v>
+        <v>3.30634891395811</v>
       </c>
       <c r="G25">
-        <v>-1.925437610127231</v>
+        <v>-5.836337340763091</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.338465294026121</v>
       </c>
       <c r="E26">
-        <v>-30.40955186285349</v>
+        <v>-32.50215064484994</v>
       </c>
       <c r="F26">
-        <v>5.337754238339051</v>
+        <v>3.034963484582491</v>
       </c>
       <c r="G26">
-        <v>-1.461719564804898</v>
+        <v>-2.720097650828348</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.604990984331319</v>
       </c>
       <c r="E27">
-        <v>-30.78398873617771</v>
+        <v>-31.47860004302925</v>
       </c>
       <c r="F27">
-        <v>5.253049727451772</v>
+        <v>3.020339544159323</v>
       </c>
       <c r="G27">
-        <v>-1.379863015800879</v>
+        <v>-4.021383717586291</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.873779348894803</v>
       </c>
       <c r="E28">
-        <v>-30.55856809278689</v>
+        <v>-32.14360192258163</v>
       </c>
       <c r="F28">
-        <v>5.039160741336182</v>
+        <v>3.21257451929311</v>
       </c>
       <c r="G28">
-        <v>-1.908126767502382</v>
+        <v>-3.387910828646749</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.133038906732625</v>
       </c>
       <c r="E29">
-        <v>-31.23617950821363</v>
+        <v>-31.250561941662</v>
       </c>
       <c r="F29">
-        <v>5.240606550074165</v>
+        <v>3.112167564254249</v>
       </c>
       <c r="G29">
-        <v>-2.322362088649229</v>
+        <v>-3.703756736366456</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.369811367828654</v>
       </c>
       <c r="E30">
-        <v>-29.90776524348556</v>
+        <v>-32.04775224173528</v>
       </c>
       <c r="F30">
-        <v>4.915492313811346</v>
+        <v>2.683198645174659</v>
       </c>
       <c r="G30">
-        <v>-1.580985278402682</v>
+        <v>-4.28366499848059</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.578092818372305</v>
       </c>
       <c r="E31">
-        <v>-29.40869118004822</v>
+        <v>-31.70681022640879</v>
       </c>
       <c r="F31">
-        <v>4.901931040057439</v>
+        <v>2.714647877243455</v>
       </c>
       <c r="G31">
-        <v>-1.837300956235214</v>
+        <v>-4.328483163991243</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.755208757214314</v>
       </c>
       <c r="E32">
-        <v>-29.65112077181185</v>
+        <v>-30.93189096150523</v>
       </c>
       <c r="F32">
-        <v>4.665070399638399</v>
+        <v>3.103172114654553</v>
       </c>
       <c r="G32">
-        <v>-2.592078854824731</v>
+        <v>-4.049559770671028</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.899127378684911</v>
       </c>
       <c r="E33">
-        <v>-29.78291295085708</v>
+        <v>-30.25578299944903</v>
       </c>
       <c r="F33">
-        <v>5.117455994383677</v>
+        <v>3.271909645120964</v>
       </c>
       <c r="G33">
-        <v>-2.277911393693434</v>
+        <v>-4.642882363310289</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.004595192314202</v>
       </c>
       <c r="E34">
-        <v>-30.30981222283455</v>
+        <v>-29.11098929878397</v>
       </c>
       <c r="F34">
-        <v>5.447842387638993</v>
+        <v>2.917773997957719</v>
       </c>
       <c r="G34">
-        <v>-1.781531506080652</v>
+        <v>-5.013646910980965</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.070149422732403</v>
       </c>
       <c r="E35">
-        <v>-29.38013915142986</v>
+        <v>-31.50009897338066</v>
       </c>
       <c r="F35">
-        <v>5.345435212028932</v>
+        <v>2.71558384743948</v>
       </c>
       <c r="G35">
-        <v>-2.053323984309277</v>
+        <v>-4.956831328435993</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.094283231723542</v>
       </c>
       <c r="E36">
-        <v>-29.00738687043649</v>
+        <v>-30.90922368485984</v>
       </c>
       <c r="F36">
-        <v>5.034303515293529</v>
+        <v>3.215659578416386</v>
       </c>
       <c r="G36">
-        <v>-2.683373769161213</v>
+        <v>-4.969682866219444</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.080873578538963</v>
       </c>
       <c r="E37">
-        <v>-27.20888077592017</v>
+        <v>-27.62873371506732</v>
       </c>
       <c r="F37">
-        <v>5.295923813994548</v>
+        <v>2.922756336767691</v>
       </c>
       <c r="G37">
-        <v>-2.786328424887007</v>
+        <v>-3.953981010406729</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.029697900411842</v>
       </c>
       <c r="E38">
-        <v>-27.58285574489561</v>
+        <v>-30.70145276891391</v>
       </c>
       <c r="F38">
-        <v>5.269898774686133</v>
+        <v>2.932888887214673</v>
       </c>
       <c r="G38">
-        <v>-2.505988118075984</v>
+        <v>-4.405271267774639</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.937725460503556</v>
       </c>
       <c r="E39">
-        <v>-26.04534372133736</v>
+        <v>-28.98966242317047</v>
       </c>
       <c r="F39">
-        <v>5.25623456004772</v>
+        <v>3.012481195406913</v>
       </c>
       <c r="G39">
-        <v>-2.243491651721632</v>
+        <v>-4.429597156397203</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.807276313747672</v>
       </c>
       <c r="E40">
-        <v>-26.24972733872555</v>
+        <v>-27.69412487973808</v>
       </c>
       <c r="F40">
-        <v>5.13519666804843</v>
+        <v>3.563273524619852</v>
       </c>
       <c r="G40">
-        <v>-3.308384903702377</v>
+        <v>-4.127109299928455</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.64230982937049</v>
       </c>
       <c r="E41">
-        <v>-25.67981435638623</v>
+        <v>-26.98438620546392</v>
       </c>
       <c r="F41">
-        <v>5.670975465183004</v>
+        <v>3.30802289111073</v>
       </c>
       <c r="G41">
-        <v>-3.611051529630245</v>
+        <v>-6.254532074374906</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.449116302348988</v>
       </c>
       <c r="E42">
-        <v>-26.56129540740129</v>
+        <v>-24.98753294941164</v>
       </c>
       <c r="F42">
-        <v>5.594637672646991</v>
+        <v>2.955299909624056</v>
       </c>
       <c r="G42">
-        <v>-2.671141303393605</v>
+        <v>-4.598656785451165</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.230565158525852</v>
       </c>
       <c r="E43">
-        <v>-24.75453390476898</v>
+        <v>-25.88613163217569</v>
       </c>
       <c r="F43">
-        <v>5.927279263125892</v>
+        <v>3.603548749755392</v>
       </c>
       <c r="G43">
-        <v>-3.792373419361667</v>
+        <v>-4.201695890928235</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.990716930917402</v>
       </c>
       <c r="E44">
-        <v>-22.72971279324533</v>
+        <v>-24.79425767876427</v>
       </c>
       <c r="F44">
-        <v>5.574321893163733</v>
+        <v>2.635076157228116</v>
       </c>
       <c r="G44">
-        <v>-3.411097889603805</v>
+        <v>-5.852360381173163</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.734362015356325</v>
       </c>
       <c r="E45">
-        <v>-22.17498378425372</v>
+        <v>-24.38437643938201</v>
       </c>
       <c r="F45">
-        <v>6.053779356827533</v>
+        <v>2.869827301367789</v>
       </c>
       <c r="G45">
-        <v>-4.185295448326686</v>
+        <v>-5.420208387567781</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.473324530656121</v>
       </c>
       <c r="E46">
-        <v>-21.64154766004619</v>
+        <v>-22.47282604821221</v>
       </c>
       <c r="F46">
-        <v>5.886367388212345</v>
+        <v>2.744404127688647</v>
       </c>
       <c r="G46">
-        <v>-4.424306904625448</v>
+        <v>-6.016570061012093</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.215294981510686</v>
       </c>
       <c r="E47">
-        <v>-21.21306344944042</v>
+        <v>-24.38422247126575</v>
       </c>
       <c r="F47">
-        <v>5.809095209186224</v>
+        <v>3.048893761814697</v>
       </c>
       <c r="G47">
-        <v>-3.039191203722079</v>
+        <v>-5.379220523246064</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.96322704076775</v>
       </c>
       <c r="E48">
-        <v>-21.40469941249701</v>
+        <v>-21.02252337709368</v>
       </c>
       <c r="F48">
-        <v>5.962329842446398</v>
+        <v>3.539719066539521</v>
       </c>
       <c r="G48">
-        <v>-4.430130154229026</v>
+        <v>-5.462987257026244</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.721571370676723</v>
       </c>
       <c r="E49">
-        <v>-21.23256305851745</v>
+        <v>-23.19824682797493</v>
       </c>
       <c r="F49">
-        <v>5.713535977954523</v>
+        <v>3.376412063657152</v>
       </c>
       <c r="G49">
-        <v>-3.973089479259403</v>
+        <v>-4.000514038506726</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.493832910206275</v>
       </c>
       <c r="E50">
-        <v>-18.52416879553595</v>
+        <v>-21.6377799696718</v>
       </c>
       <c r="F50">
-        <v>5.913605546251988</v>
+        <v>3.313854096291378</v>
       </c>
       <c r="G50">
-        <v>-4.386086656374562</v>
+        <v>-5.624919281534154</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.286392604262544</v>
       </c>
       <c r="E51">
-        <v>-19.33095266779449</v>
+        <v>-21.33801310426006</v>
       </c>
       <c r="F51">
-        <v>5.648556524244042</v>
+        <v>3.678746274032288</v>
       </c>
       <c r="G51">
-        <v>-4.848712221668936</v>
+        <v>-5.691024254862321</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.099594431679039</v>
       </c>
       <c r="E52">
-        <v>-19.75174300106123</v>
+        <v>-18.12790467749475</v>
       </c>
       <c r="F52">
-        <v>5.793129869852678</v>
+        <v>3.861547113027802</v>
       </c>
       <c r="G52">
-        <v>-4.134822871034958</v>
+        <v>-5.475031021698112</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.931513886548968</v>
       </c>
       <c r="E53">
-        <v>-18.53532242701684</v>
+        <v>-19.74825154760131</v>
       </c>
       <c r="F53">
-        <v>6.017542581776364</v>
+        <v>3.434313935631533</v>
       </c>
       <c r="G53">
-        <v>-4.372030080014817</v>
+        <v>-3.620493205508247</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.780643276952453</v>
       </c>
       <c r="E54">
-        <v>-18.92247978382861</v>
+        <v>-18.94023140193868</v>
       </c>
       <c r="F54">
-        <v>5.921547831417917</v>
+        <v>3.263482745944911</v>
       </c>
       <c r="G54">
-        <v>-4.145929751319212</v>
+        <v>-5.080956922885427</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.649309980530263</v>
       </c>
       <c r="E55">
-        <v>-16.72818053256789</v>
+        <v>-18.7512581815986</v>
       </c>
       <c r="F55">
-        <v>5.763836061534795</v>
+        <v>2.877186782756836</v>
       </c>
       <c r="G55">
-        <v>-4.686038634960228</v>
+        <v>-5.198266104069502</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.537390818512463</v>
       </c>
       <c r="E56">
-        <v>-15.31663707048101</v>
+        <v>-17.66663884354746</v>
       </c>
       <c r="F56">
-        <v>6.078508924697121</v>
+        <v>3.861399828377666</v>
       </c>
       <c r="G56">
-        <v>-5.044799144505507</v>
+        <v>-4.436224868566824</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.440402951284462</v>
       </c>
       <c r="E57">
-        <v>-17.17425786469346</v>
+        <v>-16.45671662970409</v>
       </c>
       <c r="F57">
-        <v>5.947064501127477</v>
+        <v>3.060423140879096</v>
       </c>
       <c r="G57">
-        <v>-5.035188630805003</v>
+        <v>-5.812945025982601</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.355144501551325</v>
       </c>
       <c r="E58">
-        <v>-14.80121068740198</v>
+        <v>-19.15825931151198</v>
       </c>
       <c r="F58">
-        <v>5.784766318913243</v>
+        <v>3.584864187365038</v>
       </c>
       <c r="G58">
-        <v>-5.094228899952365</v>
+        <v>-4.379594676572051</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.278635480883737</v>
       </c>
       <c r="E59">
-        <v>-15.58895685493227</v>
+        <v>-17.91642946981056</v>
       </c>
       <c r="F59">
-        <v>6.101694379299154</v>
+        <v>3.056981747924846</v>
       </c>
       <c r="G59">
-        <v>-6.13941116379229</v>
+        <v>-5.796534651744434</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.213198572887679</v>
       </c>
       <c r="E60">
-        <v>-14.71983853795815</v>
+        <v>-16.55359880262419</v>
       </c>
       <c r="F60">
-        <v>5.854823133788623</v>
+        <v>3.736757421714835</v>
       </c>
       <c r="G60">
-        <v>-4.776777377646112</v>
+        <v>-5.19800126042636</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.1574067982198</v>
       </c>
       <c r="E61">
-        <v>-15.17348295015054</v>
+        <v>-16.63092249630516</v>
       </c>
       <c r="F61">
-        <v>5.970101087373459</v>
+        <v>3.141306169392419</v>
       </c>
       <c r="G61">
-        <v>-5.364041671948506</v>
+        <v>-6.81522593017911</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.107897878223401</v>
       </c>
       <c r="E62">
-        <v>-15.39127085060143</v>
+        <v>-15.17072058100586</v>
       </c>
       <c r="F62">
-        <v>5.886329379270375</v>
+        <v>2.982566574370177</v>
       </c>
       <c r="G62">
-        <v>-5.552497787317058</v>
+        <v>-5.785712478376556</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.064638727686388</v>
       </c>
       <c r="E63">
-        <v>-14.69769882853465</v>
+        <v>-16.11350811313676</v>
       </c>
       <c r="F63">
-        <v>5.866228983791618</v>
+        <v>3.028783864100447</v>
       </c>
       <c r="G63">
-        <v>-5.682102334633986</v>
+        <v>-6.310407461986725</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.029348447588657</v>
       </c>
       <c r="E64">
-        <v>-12.6928935721249</v>
+        <v>-15.0348980600938</v>
       </c>
       <c r="F64">
-        <v>6.028522414888106</v>
+        <v>2.947972102353318</v>
       </c>
       <c r="G64">
-        <v>-5.693073482551131</v>
+        <v>-6.616771967281959</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.003726008821643</v>
       </c>
       <c r="E65">
-        <v>-12.481001744832</v>
+        <v>-15.34019419226891</v>
       </c>
       <c r="F65">
-        <v>5.763706197649729</v>
+        <v>3.671443806056197</v>
       </c>
       <c r="G65">
-        <v>-4.884522392767232</v>
+        <v>-5.544413435110157</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.9855723352012</v>
       </c>
       <c r="E66">
-        <v>-13.25639423526936</v>
+        <v>-16.36407310845517</v>
       </c>
       <c r="F66">
-        <v>5.583882725775242</v>
+        <v>3.143010236957432</v>
       </c>
       <c r="G66">
-        <v>-5.242206975012248</v>
+        <v>-6.506643359372564</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.973230735808721</v>
       </c>
       <c r="E67">
-        <v>-12.98816366284703</v>
+        <v>-14.84288623369457</v>
       </c>
       <c r="F67">
-        <v>6.033444572873291</v>
+        <v>2.684033258192095</v>
       </c>
       <c r="G67">
-        <v>-5.245279161272692</v>
+        <v>-6.522957727790092</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.964669876486661</v>
       </c>
       <c r="E68">
-        <v>-11.895338729894</v>
+        <v>-13.95984285914687</v>
       </c>
       <c r="F68">
-        <v>5.443058012068451</v>
+        <v>2.651179278976304</v>
       </c>
       <c r="G68">
-        <v>-5.256942213207545</v>
+        <v>-5.750567726931653</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.962036643423058</v>
       </c>
       <c r="E69">
-        <v>-13.13239103151732</v>
+        <v>-14.71540969037865</v>
       </c>
       <c r="F69">
-        <v>5.618968146625887</v>
+        <v>2.584959783534034</v>
       </c>
       <c r="G69">
-        <v>-5.859213210439455</v>
+        <v>-7.056601115992911</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.964565525042044</v>
       </c>
       <c r="E70">
-        <v>-12.61814205168029</v>
+        <v>-14.42239477971234</v>
       </c>
       <c r="F70">
-        <v>5.180227762048035</v>
+        <v>2.274090981980594</v>
       </c>
       <c r="G70">
-        <v>-4.890461511464684</v>
+        <v>-6.479741866320446</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.968391924884744</v>
       </c>
       <c r="E71">
-        <v>-12.06153825444951</v>
+        <v>-14.26435103684464</v>
       </c>
       <c r="F71">
-        <v>4.837961990721008</v>
+        <v>2.566717075094087</v>
       </c>
       <c r="G71">
-        <v>-5.461017482430377</v>
+        <v>-7.314055621490953</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.972819259942474</v>
       </c>
       <c r="E72">
-        <v>-12.0999080147165</v>
+        <v>-12.89679264279427</v>
       </c>
       <c r="F72">
-        <v>5.12218494024718</v>
+        <v>2.501327441551508</v>
       </c>
       <c r="G72">
-        <v>-6.01822202323619</v>
+        <v>-8.071710384154096</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.976496281209</v>
       </c>
       <c r="E73">
-        <v>-13.193009184584</v>
+        <v>-14.50385749863632</v>
       </c>
       <c r="F73">
-        <v>4.989389615531667</v>
+        <v>1.866250283518881</v>
       </c>
       <c r="G73">
-        <v>-5.320994648301363</v>
+        <v>-7.047364693938345</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.979529258652684</v>
       </c>
       <c r="E74">
-        <v>-12.23890952438194</v>
+        <v>-14.18713602653986</v>
       </c>
       <c r="F74">
-        <v>5.224672884858927</v>
+        <v>2.580796220682344</v>
       </c>
       <c r="G74">
-        <v>-6.037621820096319</v>
+        <v>-5.808638006236009</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.978260771915338</v>
       </c>
       <c r="E75">
-        <v>-11.26407851017276</v>
+        <v>-15.3302677772441</v>
       </c>
       <c r="F75">
-        <v>4.718431786753216</v>
+        <v>2.690135277084283</v>
       </c>
       <c r="G75">
-        <v>-5.114684760839522</v>
+        <v>-5.260954594401141</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.968365746099025</v>
       </c>
       <c r="E76">
-        <v>-11.57879386828383</v>
+        <v>-14.00257353988324</v>
       </c>
       <c r="F76">
-        <v>4.812690795428341</v>
+        <v>2.405453052842634</v>
       </c>
       <c r="G76">
-        <v>-4.533117915410213</v>
+        <v>-6.489971452036794</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.946384928798926</v>
       </c>
       <c r="E77">
-        <v>-13.51353910332091</v>
+        <v>-14.86593163791961</v>
       </c>
       <c r="F77">
-        <v>4.469574574024723</v>
+        <v>2.778189325982717</v>
       </c>
       <c r="G77">
-        <v>-5.002424161602836</v>
+        <v>-5.987642514089941</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.911594202817132</v>
       </c>
       <c r="E78">
-        <v>-13.68871859183364</v>
+        <v>-15.39217654540296</v>
       </c>
       <c r="F78">
-        <v>4.574040567324855</v>
+        <v>2.209339581921937</v>
       </c>
       <c r="G78">
-        <v>-4.246821937174041</v>
+        <v>-5.079477109029373</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.862671915402445</v>
       </c>
       <c r="E79">
-        <v>-12.23732003000525</v>
+        <v>-16.14400285710441</v>
       </c>
       <c r="F79">
-        <v>4.292535257149578</v>
+        <v>2.383545648914361</v>
       </c>
       <c r="G79">
-        <v>-4.415947777138788</v>
+        <v>-4.43738355950557</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.796764785994625</v>
       </c>
       <c r="E80">
-        <v>-14.1976692570817</v>
+        <v>-16.85963307606255</v>
       </c>
       <c r="F80">
-        <v>4.812608442720738</v>
+        <v>1.394177640538775</v>
       </c>
       <c r="G80">
-        <v>-4.353689657727254</v>
+        <v>-6.134584388396032</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.714065103342588</v>
       </c>
       <c r="E81">
-        <v>-15.39142029024368</v>
+        <v>-16.34633054729311</v>
       </c>
       <c r="F81">
-        <v>3.895070999845824</v>
+        <v>1.797639392144298</v>
       </c>
       <c r="G81">
-        <v>-3.487237126461503</v>
+        <v>-7.127850677089106</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.616192367143273</v>
       </c>
       <c r="E82">
-        <v>-14.88568031306706</v>
+        <v>-16.24593427854306</v>
       </c>
       <c r="F82">
-        <v>4.503774703268638</v>
+        <v>1.898025759006258</v>
       </c>
       <c r="G82">
-        <v>-3.727662185705534</v>
+        <v>-4.256290097416357</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.509644686208063</v>
       </c>
       <c r="E83">
-        <v>-15.48977874569028</v>
+        <v>-16.65849637453786</v>
       </c>
       <c r="F83">
-        <v>4.206380071643757</v>
+        <v>1.793114744343888</v>
       </c>
       <c r="G83">
-        <v>-3.345621919928099</v>
+        <v>-4.714439805141636</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.399917818744621</v>
       </c>
       <c r="E84">
-        <v>-17.31580890522522</v>
+        <v>-19.64839869573218</v>
       </c>
       <c r="F84">
-        <v>4.254369528293402</v>
+        <v>1.806292761266259</v>
       </c>
       <c r="G84">
-        <v>-3.296887379044488</v>
+        <v>-4.943870542649747</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.292429396136327</v>
       </c>
       <c r="E85">
-        <v>-17.51900153394939</v>
+        <v>-17.69034540497762</v>
       </c>
       <c r="F85">
-        <v>3.914194248774756</v>
+        <v>2.288049765919277</v>
       </c>
       <c r="G85">
-        <v>-2.946919678451513</v>
+        <v>-6.359115518506022</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.197480599195482</v>
       </c>
       <c r="E86">
-        <v>-18.13131461842253</v>
+        <v>-21.03367248010056</v>
       </c>
       <c r="F86">
-        <v>3.972903810766011</v>
+        <v>1.857935827462824</v>
       </c>
       <c r="G86">
-        <v>-2.372291736472517</v>
+        <v>-4.609283636632226</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.127938675266281</v>
       </c>
       <c r="E87">
-        <v>-18.96678184504565</v>
+        <v>-23.24814155459145</v>
       </c>
       <c r="F87">
-        <v>3.776418168955185</v>
+        <v>2.057837522933253</v>
       </c>
       <c r="G87">
-        <v>-2.265086340274298</v>
+        <v>-4.527135759620751</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.09704585317125</v>
       </c>
       <c r="E88">
-        <v>-20.99622652853114</v>
+        <v>-22.20430565345339</v>
       </c>
       <c r="F88">
-        <v>3.835075468651232</v>
+        <v>0.8905322364284686</v>
       </c>
       <c r="G88">
-        <v>-2.023899855556235</v>
+        <v>-3.664884310644334</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.113578128521965</v>
       </c>
       <c r="E89">
-        <v>-21.7416858057778</v>
+        <v>-23.8648925435921</v>
       </c>
       <c r="F89">
-        <v>3.302630372468659</v>
+        <v>1.415465815454112</v>
       </c>
       <c r="G89">
-        <v>-2.2191094838249</v>
+        <v>-2.39148959005475</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.185922647584537</v>
       </c>
       <c r="E90">
-        <v>-23.25387460268515</v>
+        <v>-25.59005094460619</v>
       </c>
       <c r="F90">
-        <v>3.023760348936673</v>
+        <v>1.023287968496096</v>
       </c>
       <c r="G90">
-        <v>-2.380746869779816</v>
+        <v>-3.130062368229535</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.321526912284411</v>
       </c>
       <c r="E91">
-        <v>-23.16420628885928</v>
+        <v>-26.15063979896372</v>
       </c>
       <c r="F91">
-        <v>3.441662331079173</v>
+        <v>0.7307157213837276</v>
       </c>
       <c r="G91">
-        <v>-1.780756838424463</v>
+        <v>-4.248070012842346</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.527921892007337</v>
       </c>
       <c r="E92">
-        <v>-24.97459057069771</v>
+        <v>-29.25197880853878</v>
       </c>
       <c r="F92">
-        <v>3.189740647404304</v>
+        <v>0.3572287716397273</v>
       </c>
       <c r="G92">
-        <v>-0.8332787050850488</v>
+        <v>-3.016868195150774</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.806390147355021</v>
       </c>
       <c r="E93">
-        <v>-28.24490053092099</v>
+        <v>-29.32487818311426</v>
       </c>
       <c r="F93">
-        <v>2.414865017098091</v>
+        <v>-0.1025068022591053</v>
       </c>
       <c r="G93">
-        <v>-2.321054423161216</v>
+        <v>-3.194075076776882</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.148507984796407</v>
       </c>
       <c r="E94">
-        <v>-28.88200248211211</v>
+        <v>-32.79748866268219</v>
       </c>
       <c r="F94">
-        <v>2.39882207617469</v>
+        <v>0.1242949300380202</v>
       </c>
       <c r="G94">
-        <v>-1.482211841692987</v>
+        <v>-4.208833427110904</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.549705141501523</v>
       </c>
       <c r="E95">
-        <v>-30.21198359884685</v>
+        <v>-32.07300754127606</v>
       </c>
       <c r="F95">
-        <v>1.774447602718603</v>
+        <v>-0.1754269574295992</v>
       </c>
       <c r="G95">
-        <v>-2.1767742274687</v>
+        <v>-2.974863993348501</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.00536108886316</v>
       </c>
       <c r="E96">
-        <v>-34.15035668705168</v>
+        <v>-37.44893791050485</v>
       </c>
       <c r="F96">
-        <v>1.560555449191182</v>
+        <v>-0.858145948663433</v>
       </c>
       <c r="G96">
-        <v>-1.646246062618335</v>
+        <v>-4.036301035786247</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.501251366923418</v>
       </c>
       <c r="E97">
-        <v>-34.80241165941614</v>
+        <v>-37.33223234261617</v>
       </c>
       <c r="F97">
-        <v>1.29101503720705</v>
+        <v>-0.4179723102321083</v>
       </c>
       <c r="G97">
-        <v>-1.480364557282074</v>
+        <v>-4.148660951389111</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.034389552144677</v>
       </c>
       <c r="E98">
-        <v>-36.91746940825364</v>
+        <v>-40.06273914417712</v>
       </c>
       <c r="F98">
-        <v>0.8715705255029121</v>
+        <v>-0.7576693105642927</v>
       </c>
       <c r="G98">
-        <v>-2.26998263712688</v>
+        <v>-4.216517203307553</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.575586330884987</v>
       </c>
       <c r="E99">
-        <v>-39.11821267802727</v>
+        <v>-41.6793862510194</v>
       </c>
       <c r="F99">
-        <v>0.4258064051900863</v>
+        <v>-1.069502589020235</v>
       </c>
       <c r="G99">
-        <v>-2.445746120897866</v>
+        <v>-4.476527449961911</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.141028221047075</v>
       </c>
       <c r="E100">
-        <v>-41.33210890055618</v>
+        <v>-43.20928364553375</v>
       </c>
       <c r="F100">
-        <v>0.2771573924080666</v>
+        <v>-1.208328665861742</v>
       </c>
       <c r="G100">
-        <v>-1.590920225566035</v>
+        <v>-4.821264488602838</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.683998276733035</v>
       </c>
       <c r="E101">
-        <v>-43.05176520565094</v>
+        <v>-44.24035604268119</v>
       </c>
       <c r="F101">
-        <v>-0.0592993456211286</v>
+        <v>-2.242974034506783</v>
       </c>
       <c r="G101">
-        <v>-2.140401263628727</v>
+        <v>-5.297559296428862</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.263402201241815</v>
       </c>
       <c r="E102">
-        <v>-44.95612438009656</v>
+        <v>-46.28462242159378</v>
       </c>
       <c r="F102">
-        <v>0.2435646143827227</v>
+        <v>-1.93642637454362</v>
       </c>
       <c r="G102">
-        <v>-2.130655017561113</v>
+        <v>-5.259021235806206</v>
       </c>
     </row>
   </sheetData>
